--- a/api/templates/rif_resistance_rate/es.xlsx
+++ b/api/templates/rif_resistance_rate/es.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25225"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-20.04\home\ubuntu\aspect\api\templates\rif_resistance_rate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-18.04\home\nsabaj\Repositories\aspect\api\templates\rif_resistance_rate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46BB0F24-DC45-43B7-BF0B-92D798AABBA2}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{209C05FB-3FE1-4BC0-BE2C-5606CE41745E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5623" yWindow="3823" windowWidth="20734" windowHeight="11143" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rif Resistance Report" sheetId="6" r:id="rId1"/>
@@ -56,24 +56,9 @@
     <t>&lt;rifResistanceRate&gt;</t>
   </si>
   <si>
-    <t>Dispositivos</t>
-  </si>
-  <si>
-    <t>Estados</t>
-  </si>
-  <si>
-    <t>Ciudades</t>
-  </si>
-  <si>
     <t>Total de resultados</t>
   </si>
   <si>
-    <t>Resultados Positivos</t>
-  </si>
-  <si>
-    <t>Resultados Negativos</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tasa de resistencia RIF </t>
   </si>
   <si>
@@ -87,6 +72,21 @@
   </si>
   <si>
     <t>Ciudades: &lt;Lgas&gt;</t>
+  </si>
+  <si>
+    <t>MTB Detectado</t>
+  </si>
+  <si>
+    <t>Resistencia RIF Detectada</t>
+  </si>
+  <si>
+    <t>Dispositivo</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>Ciudad</t>
   </si>
 </sst>
 </file>
@@ -669,43 +669,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.9" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.140625" customWidth="1"/>
-    <col min="2" max="2" width="29.140625" customWidth="1"/>
-    <col min="3" max="3" width="27.140625" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="13.640625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="39.09765625" customWidth="1"/>
+    <col min="2" max="2" width="29.09765625" customWidth="1"/>
+    <col min="3" max="3" width="27.09765625" customWidth="1"/>
+    <col min="4" max="4" width="12.8984375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="13.59765625" style="3" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="3" customWidth="1"/>
-    <col min="7" max="7" width="15.640625" style="5" customWidth="1"/>
-    <col min="8" max="8" width="13.35546875" customWidth="1"/>
-    <col min="9" max="9" width="14.35546875" customWidth="1"/>
+    <col min="7" max="7" width="15.59765625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="13.3984375" customWidth="1"/>
+    <col min="9" max="9" width="14.3984375" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="20.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.3" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -713,30 +713,30 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:7" s="8" customFormat="1" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:7" s="8" customFormat="1" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="E7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>1</v>
       </c>
